--- a/sample-data/sample-run/Tech Review.xlsx
+++ b/sample-data/sample-run/Tech Review.xlsx
@@ -39,7 +39,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,6 +114,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -552,24 +566,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>'Loss Selection' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>1 period(s) &gt; 10.0x median (1,539,016)</t>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>'Loss Selection' IBNR &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Below tolerance in periods: ['2002']</t>
         </is>
       </c>
     </row>
@@ -586,12 +600,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>'Count Selection' IBNR &gt;= 0</t>
+          <t>'Loss Selection' no extreme outlier ultimates</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
+          <t>1 period(s) &gt; 10.0x median (1,523,948)</t>
         </is>
       </c>
     </row>
@@ -608,12 +622,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>'Count Selection' no extreme outlier ultimates</t>
+          <t>'Count Selection' IBNR &gt;= 0</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1 period(s) &gt; 10.0x median (346)</t>
+          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
         </is>
       </c>
     </row>
@@ -625,17 +639,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>6. Sel - Sheet Consistency</t>
+          <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Sel - sheets present</t>
+          <t>'Count Selection' no extreme outlier ultimates</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
+          <t>1 period(s) &gt; 10.0x median (346)</t>
         </is>
       </c>
     </row>
@@ -647,12 +661,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>7. X-to-Ult Triangles</t>
+          <t>6. Sel - Sheet Consistency</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>X-to-Ult triangles</t>
+          <t>Sel - sheets present</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -669,12 +683,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>8. Average IBNR / Unpaid</t>
+          <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Average IBNR has data</t>
+          <t>X-to-Ult triangles</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -696,7 +710,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Average Unpaid has data</t>
+          <t>Average IBNR has data</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -713,12 +727,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>9. Diagnostics</t>
+          <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Average Unpaid has data</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -735,12 +749,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>10. CL Triangle Integrity</t>
+          <t>9. Diagnostics</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>CL triangles present</t>
+          <t>Diagnostics</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -757,12 +771,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>11. Development Factors</t>
+          <t>10. CL Triangle Integrity</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Development factor checks</t>
+          <t>CL triangles present</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -779,17 +793,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>12. Paid-to-Incurred Raw Data</t>
+          <t>11. Development Factors</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Paid and Incurred present</t>
+          <t>Development factor checks</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>One or both missing — skipping</t>
+          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
         </is>
       </c>
     </row>
@@ -801,17 +815,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>13. Case Reserve Reasonableness</t>
+          <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Case reserves check</t>
+          <t>Paid and Incurred present</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Incurred Loss and/or Paid Loss missing — skipping</t>
+          <t>One or both missing — skipping</t>
         </is>
       </c>
     </row>
@@ -823,17 +837,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>14. Closure Rate Checks</t>
+          <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Closure rate checks</t>
+          <t>Case reserves check</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Reported Count and/or Closed Count missing — skipping</t>
+          <t>Incurred Loss and/or Paid Loss missing — skipping</t>
         </is>
       </c>
     </row>
@@ -845,15 +859,37 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>14. Closure Rate Checks</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Closure rate checks</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Reported Count and/or Closed Count missing — skipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Trend checks</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Diagnostics sheet missing — skipping</t>
         </is>
@@ -902,44 +938,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>File readable</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>15 sheets</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Measure sheets present</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Loss Selection, Count Selection</t>
         </is>
@@ -990,209 +1026,209 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>No duplicate sheet names</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>All measure sheets same periods</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>25 periods</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Period sequence (non-integer — consecutive check skipped)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>25 periods</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>All current ages &gt; 0</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>All current ages multiples of 12</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Max current age within range</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Min current age &gt;= 11</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Maturity ordering (non-integer periods — order check skipped)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>'Loss Selection' no null Selected Ultimates</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>'Loss Selection' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1205,7 +1241,11 @@
           <t>'Loss Selection' IBNR &gt;= 0</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Below tolerance in periods: ['2002']</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1225,45 +1265,45 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1 period(s) &gt; 10.0x median (1,539,016)</t>
+          <t>1 period(s) &gt; 10.0x median (1,523,948)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>'Count Selection' no null Selected Ultimates</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr"/>
+      <c r="D18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>'Count Selection' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="D19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">

--- a/sample-data/sample-run/Tech Review.xlsx
+++ b/sample-data/sample-run/Tech Review.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -524,51 +524,51 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1. Structure</t>
+          <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Diagnostics sheet present</t>
+          <t>'Loss Selection' IBNR &gt;= 0</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
+          <t>Below tolerance in periods: ['2002']</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1. Structure</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>X-to-Ult triangle sheets present</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>'Loss Selection' most recent period has highest IBNR%</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Most recent=34.3%, max=36.4%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -578,320 +578,628 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>'Loss Selection' IBNR &gt;= 0</t>
+          <t>'Loss Selection' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Below tolerance in periods: ['2002']</t>
+          <t>6 reversal(s) (exceeds N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>'Loss Selection' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>1 period(s) &gt; 10.0x median (1,523,948)</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>'Count Selection' IBNR &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR% non-increasing as maturity increases</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>'Count Selection' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1 period(s) &gt; 10.0x median (346)</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>9 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>6. Sel - Sheet Consistency</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Sel - sheets present</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>31 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>X-to-Ult triangles</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>98 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>6 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Average IBNR has data</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Average IBNR all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>105 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Average Unpaid has data</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>9. Diagnostics</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Average IBNR non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>98 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid most-mature period final value ~= 0</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>415,456</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid &gt;= Average IBNR</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>95 cell(s) where Unpaid &lt; IBNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CL triangles present</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>31 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>5 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>6 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Development factor checks</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Paid and Incurred present</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>One or both missing — skipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Case reserves check</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Loss and/or Paid Loss missing — skipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Case reserve % of incurred non-increasing with maturity</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>14. Closure Rate Checks</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Closure rate checks</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Trend checks</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics sheet missing — skipping</t>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>YoY severity change &gt; 25% detected</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>13 period(s): ['period 3: 46%', 'period 4: 101%', 'period 6: 237%']</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Frequency spike &gt; 2x median detected</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>5 period(s) above 2x median (0.0000)</t>
         </is>
       </c>
     </row>
@@ -906,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -982,48 +1290,40 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Diagnostics sheet present</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
+      <c r="D4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>X-to-Ult triangle sheets present</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>No duplicate sheet names</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -1033,15 +1333,19 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>1. Structure</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>No duplicate sheet names</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
+          <t>All measure sheets same periods</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>24 periods</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1056,14 +1360,10 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>All measure sheets same periods</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>25 periods</t>
-        </is>
-      </c>
+          <t>Diagnostics periods in measure periods</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1078,14 +1378,10 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Period sequence (non-integer — consecutive check skipped)</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>25 periods</t>
-        </is>
-      </c>
+          <t>'Incurred-to-Ult' periods match measures</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1095,12 +1391,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>All current ages &gt; 0</t>
+          <t>'Paid-to-Ult' periods match measures</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
@@ -1113,19 +1409,15 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>All current ages multiples of 12</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
-        </is>
-      </c>
+          <t>'Reported-to-Ult' periods match measures</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1135,17 +1427,17 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Max current age within range</t>
+          <t>Period sequence consecutive</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>2001-2024</t>
         </is>
       </c>
     </row>
@@ -1157,19 +1449,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Min current age &gt;= 11</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>'Loss Selection' periods sorted ascending</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1179,12 +1467,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>3. Current Age / Maturity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Maturity ordering (non-integer periods — order check skipped)</t>
+          <t>'Count Selection' periods sorted ascending</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
@@ -1197,12 +1485,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>4. Selected Ultimate Integrity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>'Loss Selection' no null Selected Ultimates</t>
+          <t>'Incurred Loss' periods sorted ascending</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
@@ -1215,59 +1503,51 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>4. Selected Ultimate Integrity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>'Loss Selection' all Selected Ultimates &gt; 0</t>
+          <t>'Paid Loss' periods sorted ascending</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>'Loss Selection' IBNR &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Below tolerance in periods: ['2002']</t>
-        </is>
-      </c>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2. Period Consistency</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' periods sorted ascending</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>'Loss Selection' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>1 period(s) &gt; 10.0x median (1,523,948)</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>2. Period Consistency</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' contains all expected periods</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1277,12 +1557,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>4. Selected Ultimate Integrity</t>
+          <t>2. Period Consistency</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>'Count Selection' no null Selected Ultimates</t>
+          <t>'Paid Loss' contains all expected periods</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
@@ -1295,299 +1575,1565 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
+          <t>2. Period Consistency</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' contains all expected periods</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>3. Current Age / Maturity</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>All current ages &gt; 0</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>3. Current Age / Maturity</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>All current ages multiples of 12</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>3. Current Age / Maturity</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Max current age within range</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>3. Current Age / Maturity</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Min current age &gt;= 11</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>3. Current Age / Maturity</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Current age decreases as period increases (older = more mature)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>'Count Selection' all Selected Ultimates &gt; 0</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>'Loss Selection' no null Selected Ultimates</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>'Count Selection' IBNR &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>'Count Selection' no extreme outlier ultimates</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>1 period(s) &gt; 10.0x median (346)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>6. Sel - Sheet Consistency</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Sel - sheets present</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>X-to-Ult triangles</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Average IBNR has data</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Average Unpaid has data</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>9. Diagnostics</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>'Loss Selection' all Selected Ultimates &gt; 0</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>'Loss Selection' IBNR &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Below tolerance in periods: ['2002']</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>'Loss Selection' most recent period has highest IBNR%</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Most recent=34.3%, max=36.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>'Loss Selection' IBNR% non-increasing as maturity increases</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>6 reversal(s) (exceeds N/5=4 tolerance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>'Loss Selection' no extreme outlier ultimates</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>'Loss Selection' periods in plausible range (1990-2030)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>'Count Selection' no null Selected Ultimates</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>'Count Selection' all Selected Ultimates &gt; 0</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>'Count Selection' most recent period has highest IBNR%</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR% non-increasing as maturity increases</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>'Count Selection' no extreme outlier ultimates</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>4. Selected Ultimate Integrity</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>'Count Selection' periods in plausible range (1990-2030)</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>5. Cross-Measure Consistency</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Incurred Loss and Paid Loss same periods</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>5. Cross-Measure Consistency</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Paid Loss selected &lt;= Incurred Loss selected (all periods)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>5. Cross-Measure Consistency</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Incurred Loss: Unpaid &gt;= IBNR (all periods)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>6. Sel - Sheet Consistency</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Selection sheets are the primary measure sheets</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Self-comparison skipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' row count = period count</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>9 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' most-mature diagonal ~= 1.0</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>31 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' row count = period count</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' most-mature diagonal ~= 1.0</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>0.9616</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>5 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' row count = period count</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>98 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' most-mature diagonal ~= 1.0</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>0.9996</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>6 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Incurred-to-Ult &gt;= Paid-to-Ult at all cells</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Average IBNR all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>105 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Average IBNR non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Average IBNR most-mature period final value ~= 0</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>98 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid most-mature period final value ~= 0</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>415,456</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Average Unpaid &gt;= Average IBNR</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>95 cell(s) where Unpaid &lt; IBNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>9. Diagnostics</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Ultimate Severity &gt; 0 for all periods</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>9. Diagnostics</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Ultimate Severity no outliers</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Median=4,484</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>9. Diagnostics</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Loss Rate in (0, 2.0)</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Range: 0.002-0.014</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>9. Diagnostics</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Ultimate Frequency &gt; 0 for all periods</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>CL triangles present</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' diagonal = Actual in measure sheet</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>31 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' no negative values</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>'Paid Loss' diagonal = Actual in measure sheet</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>5 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>'Paid Loss' no negative values</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>'Paid Loss' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' diagonal = Actual in measure sheet</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>6 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' no negative values</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' age headers are positive integers</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Development factor checks</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Not in values file — see complete-analysis.xlsx (expected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>'Paid Loss' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>'Reported Count' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Paid and Incurred present</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>One or both missing — skipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Paid Actual &lt;= Incurred Actual for all periods</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>12. Paid-to-Incurred Raw Data</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Case reserves check</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Loss and/or Paid Loss missing — skipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Case reserves (Incurred - Paid Actual) &gt;= 0 for all periods</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Min: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>13. Case Reserve Reasonableness</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Case reserve % of incurred non-increasing with maturity</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>13. Case Reserve Reasonableness</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>Unpaid - IBNR = Incurred - Paid Actual (identity)</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>14. Closure Rate Checks</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Closure rate checks</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Trend checks</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics sheet missing — skipping</t>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>YoY severity change &gt; 25% detected</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>13 period(s): ['period 3: 46%', 'period 4: 101%', 'period 6: 237%']</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Frequency spike &gt; 2x median detected</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>5 period(s) above 2x median (0.0000)</t>
         </is>
       </c>
     </row>

--- a/sample-data/sample-run/Tech Review.xlsx
+++ b/sample-data/sample-run/Tech Review.xlsx
@@ -39,7 +39,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,11 +49,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,15 +109,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -524,7 +510,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -534,670 +520,648 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>'Loss Selection' IBNR &gt;= 0</t>
+          <t>'Loss Selection' most recent period has highest IBNR%</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Below tolerance in periods: ['2002']</t>
+          <t>Most recent=28.1%, max=35.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>'Loss Selection' most recent period has highest IBNR%</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Most recent=34.3%, max=36.4%</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>'Loss Selection' IBNR% non-increasing as maturity increases</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2 reversal(s) (within N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>'Loss Selection' IBNR% non-increasing as maturity increases</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>6 reversal(s) (exceeds N/5=4 tolerance)</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>'Count Selection' IBNR &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>'Count Selection' IBNR% non-increasing as maturity increases</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>4. Selected Ultimate Integrity</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>'Count Selection' IBNR% non-increasing as maturity increases</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>8 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred-to-Ult' all values in (0, 1]</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>9 cell(s) &gt; 1.0</t>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>31 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred-to-Ult' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>'Paid-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>5 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' all values in (0, 1]</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>98 cell(s) &gt; 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>7. X-to-Ult Triangles</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>'Reported-to-Ult' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>6 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Average IBNR all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>104 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Average IBNR non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Average Unpaid all values &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>98 cell(s) &lt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Average Unpaid non-increasing across ages</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>115 reversal(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Average Unpaid most-mature period final value ~= 0</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>415,456</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>8. Average IBNR / Unpaid</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Average Unpaid &gt;= Average IBNR</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>95 cell(s) where Unpaid &lt; IBNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>'Paid-to-Ult' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>'Paid Loss' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>'Reported-to-Ult' all values in (0, 1]</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>98 cell(s) &gt; 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>7. X-to-Ult Triangles</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>'Reported-to-Ult' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>10. CL Triangle Integrity</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>'Reported Count' non-decreasing across ages</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>6 reversal(s)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Average IBNR all values &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>105 cell(s) &lt; 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Average IBNR non-increasing across ages</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>115 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Average Unpaid all values &gt;= 0</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>98 cell(s) &lt; 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Average Unpaid non-increasing across ages</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>115 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Average Unpaid most-mature period final value ~= 0</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>415,456</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>8. Average IBNR / Unpaid</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Average Unpaid &gt;= Average IBNR</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>95 cell(s) where Unpaid &lt; IBNR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>31 reversal(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>5 reversal(s)</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>10. CL Triangle Integrity</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>'Reported Count' non-decreasing across ages</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>6 reversal(s)</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>11. Development Factors</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' link ratios within ceilings</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' link ratios &gt;= 1.0</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>'Incurred Loss' average LDFs non-increasing with age</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>'Incurred Loss' average LDFs non-increasing with age</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' link ratios within ceilings</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>'Paid Loss' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>'Paid Loss' link ratios &gt;= 1.0</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios within ceilings</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>'Reported Count' link ratios within ceilings</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>'Reported Count' link ratios &gt;= 1.0</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>11. Development Factors</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>'Reported Count' link ratios &gt;= 1.0</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>12. Paid-to-Incurred Raw Data</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Paid/Incurred ratio non-decreasing with maturity</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>12. Paid-to-Incurred Raw Data</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Paid/Incurred ratio non-decreasing with maturity</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>13. Case Reserve Reasonableness</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Case reserve % of incurred non-increasing with maturity</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>13. Case Reserve Reasonableness</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Case reserve % of incurred non-increasing with maturity</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>4 reversal(s)</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>14. Closure Rate Checks</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Closure rate checks</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>14. Closure Rate Checks</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Closure rate checks</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Reported Count and/or Closed Count missing — skipping</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>15. Severity / Frequency Trends</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>YoY severity change &gt; 25% detected</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>14 period(s): ['period 3: 45%', 'period 4: 101%', 'period 6: 232%']</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>YoY severity change &gt; 25% detected</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>13 period(s): ['period 3: 46%', 'period 4: 101%', 'period 6: 237%']</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>15. Severity / Frequency Trends</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Frequency spike &gt; 2x median detected</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>5 period(s) above 2x median (0.0000)</t>
         </is>
@@ -1246,1892 +1210,1888 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>File readable</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>15 sheets</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Measure sheets present</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Loss Selection, Count Selection</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Diagnostics sheet present</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>1. Structure</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>No duplicate sheet names</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>All measure sheets same periods</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>24 periods</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Diagnostics periods in measure periods</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' periods match measures</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' periods match measures</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' periods match measures</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Period sequence consecutive</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>2001-2024</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' periods sorted ascending</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' periods sorted ascending</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' periods sorted ascending</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' periods sorted ascending</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' periods sorted ascending</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' contains all expected periods</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' contains all expected periods</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>2. Period Consistency</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' contains all expected periods</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>All current ages &gt; 0</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>All current ages multiples of 12</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>11-month development pattern detected (ages 11, 23, 35, ...) — valid</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Max current age within range</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>287</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Min current age &gt;= 11</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>3. Current Age / Maturity</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>Current age decreases as period increases (older = more mature)</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' no null Selected Ultimates</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' IBNR &gt;= 0</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Below tolerance in periods: ['2002']</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>'Loss Selection' most recent period has highest IBNR%</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Most recent=34.3%, max=36.4%</t>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Most recent=28.1%, max=35.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>'Loss Selection' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>6 reversal(s) (exceeds N/5=4 tolerance)</t>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2 reversal(s) (within N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' no extreme outlier ultimates</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>'Loss Selection' periods in plausible range (1990-2030)</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' no null Selected Ultimates</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' all Selected Ultimates &gt; 0</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr"/>
+      <c r="D33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>'Count Selection' IBNR &gt;= 0</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Slight negatives (within tolerance) periods: ['2005', '2006', '2007', '2012', '2014', '2017', '2022']</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' most recent period has highest IBNR%</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>8.9%</t>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>'Count Selection' IBNR% non-increasing as maturity increases</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>11 reversal(s) (exceeds N/5=4 tolerance)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' no extreme outlier ultimates</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>4. Selected Ultimate Integrity</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>'Count Selection' periods in plausible range (1990-2030)</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Incurred Loss and Paid Loss same periods</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>Paid Loss selected &lt;= Incurred Loss selected (all periods)</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>5. Cross-Measure Consistency</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Incurred Loss: Unpaid &gt;= IBNR (all periods)</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>6. Sel - Sheet Consistency</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Selection sheets are the primary measure sheets</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Self-comparison skipped</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' row count = period count</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' all values in (0, 1]</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>9 cell(s) &gt; 1.0</t>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>8 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>1.0000</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>'Incurred-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' row count = period count</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' all values in (0, 1]</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr"/>
+      <c r="D48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>0.9616</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>'Paid-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' row count = period count</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' all values in (0, 1]</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>98 cell(s) &gt; 1.0</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' most-mature diagonal ~= 1.0</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>0.9996</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>'Reported-to-Ult' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>6 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>7. X-to-Ult Triangles</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Incurred-to-Ult &gt;= Paid-to-Ult at all cells</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr"/>
+      <c r="D55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Average IBNR all values &gt;= 0</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>105 cell(s) &lt; 0</t>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>104 cell(s) &lt; 0</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Average IBNR non-increasing across ages</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>115 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>Average IBNR most-mature period final value ~= 0</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid all values &gt;= 0</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>98 cell(s) &lt; 0</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid non-increasing across ages</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>115 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid most-mature period final value ~= 0</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>415,456</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>8. Average IBNR / Unpaid</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Average Unpaid &gt;= Average IBNR</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>95 cell(s) where Unpaid &lt; IBNR</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>9. Diagnostics</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Ultimate Severity &gt; 0 for all periods</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>9. Diagnostics</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>Ultimate Severity no outliers</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>Median=4,484</t>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Median=4,368</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>9. Diagnostics</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Loss Rate in (0, 2.0)</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Range: 0.002-0.014</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>9. Diagnostics</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Ultimate Frequency &gt; 0 for all periods</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr"/>
+      <c r="D66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr"/>
+      <c r="D67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>'Incurred Loss' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>31 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' no negative values</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>'Incurred Loss' age headers are positive integers</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr"/>
+      <c r="D70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>'Paid Loss' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>5 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' no negative values</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' age headers are positive integers</t>
         </is>
       </c>
-      <c r="D74" s="10" t="inlineStr"/>
+      <c r="D74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' diagonal = Actual in measure sheet</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>'Reported Count' non-decreasing across ages</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>6 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' no negative values</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>10. CL Triangle Integrity</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' age headers are positive integers</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr"/>
+      <c r="D78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>'Incurred Loss' link ratios within ceilings</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>96 violation(s): ['2001 11-&gt;23: 2.740 (ceil 1.05)', '2002 11-&gt;23: 1.430 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>'Incurred Loss' link ratios &gt;= 1.0</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>31 below 1.0: ['2006 23-&gt;35: 0.8692', '2009 23-&gt;35: 0.9424']</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>'Incurred Loss' average LDFs non-increasing with age</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>4 reversal(s) (younger age avg &lt; older age avg)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>'Paid Loss' link ratios within ceilings</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>107 violation(s): ['2001 11-&gt;23: 3.212 (ceil 1.05)', '2002 11-&gt;23: 2.549 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>'Paid Loss' link ratios &gt;= 1.0</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>5 below 1.0: ['2013 59-&gt;71: 0.9974', '2001 71-&gt;83: 0.9904']</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>'Paid Loss' average LDFs non-increasing with age</t>
         </is>
       </c>
-      <c r="D84" s="10" t="inlineStr"/>
+      <c r="D84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>'Reported Count' link ratios within ceilings</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>12 violation(s): ['2001 11-&gt;23: 1.070 (ceil 1.05)', '2004 11-&gt;23: 1.059 (ceil 1.05)']</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>'Reported Count' link ratios &gt;= 1.0</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>6 below 1.0: ['2005 35-&gt;47: 0.9979', '2003 47-&gt;59: 0.9952']</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>11. Development Factors</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>'Reported Count' average LDFs non-increasing with age</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>Paid Actual &lt;= Incurred Actual for all periods</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>12. Paid-to-Incurred Raw Data</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Paid/Incurred ratio non-decreasing with maturity</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>Case reserves (Incurred - Paid Actual) &gt;= 0 for all periods</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>Min: 0</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Case reserve % of incurred non-increasing with maturity</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D91" s="4" t="inlineStr">
         <is>
           <t>4 reversal(s)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>13. Case Reserve Reasonableness</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>Unpaid - IBNR = Incurred - Paid Actual (identity)</t>
         </is>
       </c>
-      <c r="D92" s="10" t="inlineStr"/>
+      <c r="D92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>14. Closure Rate Checks</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Closure rate checks</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>Reported Count and/or Closed Count missing — skipping</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>YoY severity change &gt; 25% detected</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>13 period(s): ['period 3: 46%', 'period 4: 101%', 'period 6: 237%']</t>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>14 period(s): ['period 3: 45%', 'period 4: 101%', 'period 6: 232%']</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>15. Severity / Frequency Trends</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Frequency spike &gt; 2x median detected</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>5 period(s) above 2x median (0.0000)</t>
         </is>
